--- a/tiflow/ti-flow-system-diagram/2.0.0-ballot.2/TIFLOW-CM-TelemetryDataStatusCodes.xlsx
+++ b/tiflow/ti-flow-system-diagram/2.0.0-ballot.2/TIFLOW-CM-TelemetryDataStatusCodes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="189">
   <si>
     <t>Property</t>
   </si>
@@ -570,22 +570,10 @@
     <t>79267</t>
   </si>
   <si>
-    <t>MSG_INTERNAL_ERROR</t>
-  </si>
-  <si>
-    <t>79268</t>
-  </si>
-  <si>
     <t>MSG_PARAM_UNKNOWN</t>
   </si>
   <si>
     <t>79269</t>
-  </si>
-  <si>
-    <t>MSG_TIMEOUT</t>
-  </si>
-  <si>
-    <t>79270</t>
   </si>
   <si>
     <t>MSG_UNKNOWN_OPERATION</t>
@@ -1973,7 +1961,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2127,32 +2115,6 @@
       </c>
       <c r="E11" s="2"/>
     </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D12" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D13" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="E13" s="2"/>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
